--- a/Mechanical/Cycloidal Drive Calculations.xlsx
+++ b/Mechanical/Cycloidal Drive Calculations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC BLDC\Mechanical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643FFDB9-8CBC-4849-990C-2AA5F638EE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C4ECA6-2862-4B16-966F-C24362BB03BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -540,14 +540,14 @@
         <v>21</v>
       </c>
       <c r="B2" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="4">
         <f>1-(B2/B3)</f>
-        <v>-6.6666666666666652E-2</v>
+        <v>-7.1428571428571397E-2</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>3</v>
@@ -559,14 +559,14 @@
       </c>
       <c r="B3" s="1">
         <f>B2-1</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="4">
         <f>B3/(B2 -B3)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>3</v>
@@ -577,8 +577,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="1">
-        <f>25-B2-1</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -607,7 +606,7 @@
       </c>
       <c r="I6" s="10">
         <f>E6/F3</f>
-        <v>906.66666666666663</v>
+        <v>971.42857142857144</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -629,7 +628,7 @@
       </c>
       <c r="I7" s="10">
         <f>E7/F3</f>
-        <v>371.73333333333329</v>
+        <v>398.28571428571422</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -678,7 +677,7 @@
       </c>
       <c r="I10" s="9">
         <f>E10*F3*B13*B14</f>
-        <v>30.333954367995801</v>
+        <v>28.311690743462744</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -700,7 +699,7 @@
       </c>
       <c r="I11" s="9">
         <f>E11*F3*B13*B14</f>
-        <v>15.166977183997901</v>
+        <v>14.155845371731372</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">

--- a/Mechanical/Cycloidal Drive Calculations.xlsx
+++ b/Mechanical/Cycloidal Drive Calculations.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC BLDC\Mechanical\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\Mechanical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C4ECA6-2862-4B16-966F-C24362BB03BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{929AFA1B-18D9-4E8D-B7BA-B6DBC12D5BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10848" yWindow="2340" windowWidth="12288" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
